--- a/MidataMiScript.xlsx
+++ b/MidataMiScript.xlsx
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Marrugo, Andres G. (24329839300)</t>
+          <t>Marrugo, Andrés G. (24329839300)</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -788,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>5</v>
@@ -845,10 +845,10 @@
         <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF3" t="n">
         <v>7</v>
@@ -872,17 +872,17 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>14622047600</t>
+          <t>57194034904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T00057322</t>
+          <t>T00014261</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORGELINA CECILIA PASQUALINO </t>
+          <t>HOLMAN OSPINA MATEUS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pasqualino, Jorgelina C.</t>
+          <t>Ospina-Mateus, Holman</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=14622047600</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57194034904</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pasqualino, Jorgelina (14622047600)</t>
+          <t>Ospina-Mateus, Holman (57194034904)</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -924,13 +924,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -939,13 +939,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -957,59 +957,59 @@
         <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
         <v>2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>57194034904</t>
+          <t>14622047600</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T00014261</t>
+          <t>T00057322</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HOLMAN OSPINA MATEUS</t>
+          <t xml:space="preserve">JORGELINA CECILIA PASQUALINO </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1019,24 +1019,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ospina-Mateus, Holman</t>
+          <t>Pasqualino, Jorgelina C.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57194034904</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=14622047600</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ospina-Mateus, Holman (57194034904)</t>
+          <t>Pasqualino, Jorgelina C. (14622047600)</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1051,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1093,50 +1093,50 @@
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AJ5" t="n">
         <v>2</v>
       </c>
       <c r="AK5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>36142156300</t>
+          <t>56674579200</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T00000080</t>
+          <t>T00020729</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LENNY ALEXANDRA ROMERO PEREZ</t>
+          <t>ROSA LEONOR ACEVEDO BARRIOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1146,27 +1146,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Romero, Lenny A.</t>
+          <t>Acevedo-Barrios, R. L.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=36142156300</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=56674579200</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Romero, Lenny A. (36142156300)</t>
+          <t>Acevedo-Barrios, R. L. (56674579200)</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1178,76 +1178,76 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>4</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1</v>
-      </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1290,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1380,271 +1380,271 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>57193012270</t>
+          <t>36142156300</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T00021680</t>
+          <t>T00000080</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIGUEL EFREN GARCES PRETTEL</t>
+          <t>LENNY ALEXANDRA ROMERO PEREZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
+          <t>CIENCIAS BÁSICAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Garcés-Prettel, Miguel</t>
+          <t>Romero, Lenny A.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57193012270</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=36142156300</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Garcés-Prettel, Miguel (57193012270)</t>
+          <t>Romero, Lenny A. (36142156300)</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5</v>
-      </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>24537991200</t>
+          <t>57193012270</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T00009693</t>
+          <t>T00021680</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAIRO FRANCISCO USECHE VIVERO</t>
+          <t>MIGUEL EFREN GARCES PRETTEL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Useche, J. F.</t>
+          <t>Garcés-Prettel, Miguel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=24537991200</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57193012270</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Useche, J. (24537991200)</t>
+          <t>Garcés-Prettel, Miguel Efrén (57193012270)</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>10</v>
       </c>
       <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>5</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3</v>
-      </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>57039103600</t>
+          <t>24537991200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T00047675</t>
+          <t>T00009693</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAURA PATRICIA MARTINEZ BUELVAS</t>
+          <t>JAIRO FRANCISCO USECHE VIVERO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1654,27 +1654,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Martínez-Buelvas, Laura Patricia</t>
+          <t>Useche, J. F.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57039103600</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=24537991200</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Martínez-Buelvas, Laura (57039103600)</t>
+          <t>Useche, J. F. (24537991200)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1686,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1698,16 +1698,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1734,64 +1734,64 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF10" t="n">
         <v>3</v>
       </c>
       <c r="AG10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>56674579200</t>
+          <t>57039103600</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T00020729</t>
+          <t>T00047675</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ROSA LEONOR ACEVEDO BARRIOS</t>
+          <t>LAURA PATRICIA MARTINEZ BUELVAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CIENCIAS BÁSICAS</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acevedo-Barrios, R. L.</t>
+          <t>Martínez-Buelvas, Laura Patricia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=56674579200</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57039103600</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acevedo-Barrios, R. (56674579200)</t>
+          <t>Martínez-Buelvas, Laura Patricia (57039103600)</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1801,7 +1801,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1828,10 +1828,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -1843,46 +1843,46 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Contreras-Ortiz, S.H. (57210822856)</t>
+          <t>Contreras-Ortiz, Sonia H. (57210822856)</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1940,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
         <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2055,10 +2055,10 @@
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2088,10 +2088,10 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -2115,10 +2115,10 @@
         <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
         <v>5</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Villa, J.L. (7005142049)</t>
+          <t>Villa, J. L. (7005142049)</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2194,7 +2194,7 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2299,11 +2299,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rubiano-Labrador, C. (55649334800)</t>
+          <t>Rubiano-Labrador, Carolina (55649334800)</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2396,17 +2396,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>26325154200</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T00090440</t>
+          <t>T00000254</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR AUGUSTO VILORIA NUÑEZ </t>
+          <t>JUAN CARLOS MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2416,21 +2416,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Viloria-Nuñez, Cesar</t>
+          <t>Martínez, Juan Carlos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=35788581800</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=26325154200</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Viloria-Nuñez, Cesar (35788581800)</t>
+          <t>Martinez-Santos, Juan Carlos (26325154200)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -2442,16 +2442,16 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2460,25 +2460,25 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2490,31 +2490,31 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AF16" t="n">
         <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
         <v>4</v>
@@ -2523,50 +2523,50 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>55872162200</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T00044492</t>
+          <t>T00090440</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MAURO ANTONIO MAZA CHAMORRO</t>
+          <t xml:space="preserve">CESAR AUGUSTO VILORIA NUÑEZ </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maza-Chamorro, Mauro Antonio</t>
+          <t>Viloria-Nuñez, Cesar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=55872162200</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=35788581800</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Maza-Chamorro, Mauro Antonio (55872162200)</t>
+          <t>Viloria-Nuñez, Cesar (35788581800)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2587,13 +2587,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2620,83 +2620,83 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>26325154200</t>
+          <t>55872162200</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T00000254</t>
+          <t>T00044492</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JUAN CARLOS MARTINEZ SANTOS</t>
+          <t>MAURO ANTONIO MAZA CHAMORRO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Martínez, Juan Carlos</t>
+          <t>Maza-Chamorro, Mauro Antonio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=26325154200</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=55872162200</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Martínez-Santos, Juan Carlos (26325154200)</t>
+          <t>Maza-Chamorro, Mauro Antonio (55872162200)</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2714,28 +2714,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2744,50 +2744,50 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>57024211000</t>
+          <t>57200615582</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T00057415</t>
+          <t>T00040553</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DEYLER RAFAEL CASTILLA CABALLERO</t>
+          <t>MILTON CESAR GUERRERO PAJARO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Castilla-Caballero, Deyler</t>
+          <t>Guerrero, Milton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57024211000</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57200615582</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Castilla-Caballero, Deyler (57024211000)</t>
+          <t>Guerrero, Milton (57200615582)</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2847,16 +2847,16 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2871,83 +2871,83 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>57206773929</t>
+          <t>57024211000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T00055756</t>
+          <t>T00057415</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TANIA LUCIA COBOS COBOS</t>
+          <t>DEYLER RAFAEL CASTILLA CABALLERO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobos, Tania Lucía</t>
+          <t>Castilla-Caballero, Deyler</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57206773929</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57024211000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cobos, Tania Lucía (57206773929)</t>
+          <t>Castilla-Caballero, Deyler Rafael (57024211000)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2968,28 +2968,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3004,64 +3004,64 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>57220077867</t>
+          <t>57206773929</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T00000060</t>
+          <t>T00055756</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VILMA VIVIANA OJEDA CAICEDO</t>
+          <t>TANIA LUCIA COBOS COBOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CIENCIAS BÁSICAS</t>
+          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ojeda-Caicedo, Vilma Viviana</t>
+          <t>Cobos, Tania Lucía</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57220077867</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57206773929</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ojeda-Caicedo, Vilma V. (57220077867)</t>
+          <t>Cobos, Tania Lucía (57206773929)</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3095,16 +3095,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3137,58 +3137,58 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>57196040759</t>
+          <t>57220077867</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T00052721</t>
+          <t>T00000060</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PEDRO VAZQUEZ MIRAZ</t>
+          <t>VILMA VIVIANA OJEDA CAICEDO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
+          <t>CIENCIAS BÁSICAS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vázquez-Miraz, Pedro</t>
+          <t>Ojeda-Caicedo, Vilma Viviana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57196040759</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57220077867</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Vázquez-Miraz, Pedro (57196040759)</t>
+          <t>Ojeda-Caicedo, Vilma Viviana (57220077867)</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3204,125 +3204,125 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
         <v>5</v>
       </c>
-      <c r="AG22" t="n">
-        <v>6</v>
-      </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>57200615582</t>
+          <t>57196040759</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T00040553</t>
+          <t>T00052721</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MILTON CESAR GUERRERO PAJARO</t>
+          <t>PEDRO VAZQUEZ MIRAZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guerrero, Milton</t>
+          <t>Vázquez-Miraz, Pedro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57200615582</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57196040759</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Guerrero, Milton (57200615582)</t>
+          <t>Vázquez-Miraz, Pedro (57196040759)</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3340,19 +3340,19 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3373,40 +3373,40 @@
         <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fajardo-Cuadro, Juan Gabriel (56581610900)</t>
+          <t>Fajardo Cuadro, Juan Gabriel (56581610900)</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3482,7 +3482,7 @@
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI24" t="n">
         <v>4</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Olite, Jorge Luis Muñiz (57758796500)</t>
+          <t>Muñiz-Olite, Jorge Luis (57758796500)</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Arias-Tapia, Mary Judith (57219403758)</t>
+          <t>Arias Tapia, Mary Judith (57219403758)</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Día, A. Palencia (56801043600)</t>
+          <t>Palencia Díaz, Argemiro (56801043600)</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3833,7 +3833,7 @@
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3893,10 +3893,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>6</v>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Toro Gonzalez, Daniel (56380539800)</t>
+          <t>Toro-González, Daniel (56380539800)</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF29" t="n">
         <v>1</v>
@@ -4220,13 +4220,13 @@
         <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4247,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
@@ -4274,10 +4274,10 @@
         <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
         <v>3</v>
@@ -4331,14 +4331,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gutiérrez-Ruiz, K. (57192930752)</t>
+          <t>Gutiérrez-Ruiz, Karol Patricia (57192930752)</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>2</v>
@@ -4350,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4401,10 +4401,10 @@
         <v>1</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF31" t="n">
         <v>1</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Muentes, J. (57350116000)</t>
+          <t>Acevedo, Jeovanny Muentes (57350116000)</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Marrugo-Salas, Lina (57392556500)</t>
+          <t>Marrugo-Salas, Lina Margarita (57392556500)</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Patiño-Vanegas, Alberto (57190688459)</t>
+          <t>Patiño, Alberto (57190688459)</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4782,10 +4782,10 @@
         <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Domínguez-De la Ossa, Elsy (57223851529)</t>
+          <t>de la Ossa, Elsy Domínguez (57223851529)</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4855,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4909,10 +4909,10 @@
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
         <v>4</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Acevedo, Oscar (57197327858)</t>
+          <t>Acevedo-Patĩno, Oscar (57197327858)</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Magre Colorado, Luz A. (56682785300)</t>
+          <t>Magre, Luz Alejandra (56682785300)</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pérez-Morón, James Manuel (57322375300)</t>
+          <t>Pérez-Morón, James (57322375300)</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cabrera, Jairo (57193252278)</t>
+          <t>Cabrera Tovar, Jairo Humberto (57193252278)</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5623,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AF41" t="n">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>4</v>
       </c>
       <c r="AE43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF43" t="n">
         <v>1</v>
@@ -6131,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="AE45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
         <v>1</v>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Jiménez-Castilla, Tania (57204842254)</t>
+          <t>Jiménez-Castilla, Tania I. (57204842254)</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -6560,10 +6560,10 @@
         <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF48" t="n">
         <v>1</v>
@@ -6587,37 +6587,37 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>57189892062</t>
+          <t>57205658483</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T00076408</t>
+          <t>T00000020</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ENRIQUE PEREIRA BATISTA</t>
+          <t>JORGE ELIECER DUQUE PARDO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CIENCIAS BÁSICAS</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pereira Batista, Enrique</t>
+          <t>Duque, Jorge Eliecer</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57189892062</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57205658483</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pereira-Batista, Enrique (57189892062)</t>
+          <t>Duque, Jorge Eliecer (57205658483)</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6681,16 +6681,16 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -6760,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -6814,10 +6814,10 @@
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Del Río Cortina, Jorge (57197807415)</t>
+          <t>Del Rio Cortina, Jorge Luis (57197807415)</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7068,10 +7068,10 @@
         <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7222,37 +7222,37 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>57205658483</t>
+          <t>57189892062</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>T00000020</t>
+          <t>T00076408</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JORGE ELIECER DUQUE PARDO</t>
+          <t>ENRIQUE PEREIRA BATISTA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>CIENCIAS BÁSICAS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Duque, Jorge Eliecer</t>
+          <t>Pereira Batista, Enrique</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57205658483</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57189892062</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Duque, J. (57205658483)</t>
+          <t>Pereira Batista, Enrique (57189892062)</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -7265,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -7316,16 +7316,16 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -7340,46 +7340,46 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>57219506381</t>
+          <t>58917134900</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T00053397</t>
+          <t>T00035572</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CARLOS RAFAEL PAYARES GUEVARA</t>
+          <t>JEFFERSON ANDRES PIEDRAHITA GONZALEZ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CIENCIAS BÁSICAS</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guevara, Carlos R.Payares</t>
+          <t>Piedrahita, Jefferson Marulanda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57225975125&amp;origin=recordpage</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=58917134900&amp;origin=recordpage</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Payares Guevara, Carlos R. (57219506381)</t>
+          <t>Piedrahita, Jefferson Marulanda (58917134900)</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -7389,7 +7389,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>1</v>
@@ -7425,10 +7425,10 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -7449,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -7476,37 +7476,37 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>57202159706</t>
+          <t>57219506381</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T00085821</t>
+          <t>T00053397</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YULANDERSON SALGUERO RODRIGUEZ</t>
+          <t>CARLOS RAFAEL PAYARES GUEVARA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>CIENCIAS BÁSICAS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salguero-Rodríguez, Yulánderson</t>
+          <t>Guevara, Carlos R.Payares</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57202159706</t>
+          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57225975125&amp;origin=recordpage</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rodríguez, Yulanderson Salguero (57202159706)</t>
+          <t>Guevara, Carlos R.Payares (57219506381)</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -7519,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -7528,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7552,13 +7552,13 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -7576,10 +7576,10 @@
         <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI56" t="n">
         <v>1</v>
@@ -7603,37 +7603,37 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>58954857900</t>
+          <t>57202159706</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T00057359</t>
+          <t>T00085821</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AUGUSTO ANDRES ALEAN ROMERO</t>
+          <t>YULANDERSON SALGUERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aleán–Romero, Andrés</t>
+          <t>Salguero-Rodríguez, Yulánderson</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=58954857900&amp;origin=recordpage</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57202159706</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Aleán–Romero, Andrés (58954857900)</t>
+          <t>Salguero-Rodríguez, Yulánderson (57202159706)</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -7658,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -7709,16 +7709,16 @@
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57" t="n">
         <v>0</v>
@@ -7730,37 +7730,37 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>57903699900</t>
+          <t>58954857900</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T00022797</t>
+          <t>T00057359</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAFAEL DAVID MENDEZ ANILLO</t>
+          <t>AUGUSTO ANDRES ALEAN ROMERO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Méndez-Anillo, Rafael D.</t>
+          <t>Aleán–Romero, Andrés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57903699900&amp;origin=recordpage</t>
+          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=58954857900&amp;origin=recordpage</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Méndez-Anillo, Rafael D. (57903699900)</t>
+          <t>Aleán–Romero, Andrés (58954857900)</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -7770,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -7815,7 +7815,7 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH58" t="n">
         <v>0</v>
@@ -7848,26 +7848,26 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>58803522300</t>
+          <t>57903699900</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T00015209</t>
+          <t>T00022797</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MAURO ANTONIO GONZALEZ SIERRA</t>
+          <t>RAFAEL DAVID MENDEZ ANILLO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7877,17 +7877,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gonzalez-Sierra, Mauro A.</t>
+          <t>Méndez-Anillo, Rafael D.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=58803522300</t>
+          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57903699900&amp;origin=recordpage</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gonzalez-Sierra, Mauro A. (58803522300)</t>
+          <t>Méndez-Anillo, Rafael D. (57903699900)</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -7897,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -7939,10 +7939,10 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -7957,28 +7957,28 @@
         <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
         <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -8111,37 +8111,37 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>57222223605</t>
+          <t>58803522300</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T00055292</t>
+          <t>T00015209</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MARCOS RICARDO POSADA LLORENTE</t>
+          <t>MAURO ANTONIO GONZALEZ SIERRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Llorente, Marcos Ricardo Posada</t>
+          <t>Gonzalez-Sierra, Mauro A.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57222223605</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=58803522300</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Llorente, Marcos Ricardo Posada (57222223605)</t>
+          <t>Gonzalez-Sierra, Mauro A. (58803522300)</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -8166,7 +8166,7 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8217,16 +8217,16 @@
         <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH61" t="n">
         <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ61" t="n">
         <v>0</v>
@@ -8238,17 +8238,17 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>58660078000</t>
+          <t>57222223605</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T00000073</t>
+          <t>T00055292</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AARÓN EDUARDO ESPINOSA ESPINOSA</t>
+          <t>MARCOS RICARDO POSADA LLORENTE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8258,17 +8258,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Espinosa-Espinos, Aaron</t>
+          <t>Llorente, Marcos Ricardo Posada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57211108028</t>
+          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57222223605</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Espinosa-Espinos, Aaron (58660078000)</t>
+          <t>Llorente, Marcos Ricardo Posada (57222223605)</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -8317,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -8350,10 +8350,10 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
         <v>0</v>
@@ -8365,44 +8365,44 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>57195913859</t>
+          <t>58660078000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T00019346</t>
+          <t>T00000073</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JULIO SEFERINO HURTADO MARQUEZ</t>
+          <t>AARÓN EDUARDO ESPINOSA ESPINOSA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CIENCIAS BÁSICAS</t>
+          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hurtado, Julio Seferino</t>
+          <t>Espinosa-Espinos, Aaron</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57195913859</t>
+          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57211108028</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hurtado, Julio (57195913859)</t>
+          <t>Espinosa-Espinos, Aaron (58660078000)</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -8477,10 +8477,10 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ63" t="n">
         <v>0</v>
@@ -8492,44 +8492,44 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>57204847841</t>
+          <t>57195913859</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T00064566</t>
+          <t>T00019346</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HAROLD ALBERTO RODRIGUEZ ARIAS</t>
+          <t>JULIO SEFERINO HURTADO MARQUEZ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>CIENCIAS BÁSICAS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodríguez-Arias, Harold A.</t>
+          <t>Hurtado, Julio Seferino</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57204847841</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57195913859</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rodríguez-Arias, H.A. (57204847841)</t>
+          <t>Hurtado, Julio Seferino (57195913859)</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8613,43 +8613,43 @@
         <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>57204847841</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T00000431</t>
+          <t>T00064566</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ELIAS RAFAEL GENEY CASTRO</t>
+          <t>HAROLD ALBERTO RODRIGUEZ ARIAS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Geney-Castro, Elías</t>
+          <t>Rodríguez-Arias, Harold A.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57427876200</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57204847841</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Geney, Elías Rafael (57427876200)</t>
+          <t>Rodríguez-Arias, Harold A. (57204847841)</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -8665,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -8716,10 +8716,10 @@
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -8731,52 +8731,52 @@
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
         <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>57212006168</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T00000057</t>
+          <t>T00000431</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EDUARDO GOMEZ VASQUEZ</t>
+          <t>ELIAS RAFAEL GENEY CASTRO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gomez, Eduardo</t>
+          <t>Geney-Castro, Elías</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57212006168</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57427876200</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gomez, Eduardo (57212006168)</t>
+          <t>Geney-Castro, Elías (57427876200)</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -8792,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -8825,7 +8825,7 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -8840,16 +8840,16 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -8858,32 +8858,32 @@
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>57209248085</t>
+          <t>57212006168</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T00021662</t>
+          <t>T00000057</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EDGARDO WILLIAM ARRIETA ORTIZ</t>
+          <t>EDUARDO GOMEZ VASQUEZ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8893,24 +8893,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arrieta, O. E.W.</t>
+          <t>Gomez, Eduardo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57209248085</t>
+          <t>https://scopus.utb.elogim.com/authid/detail.uri?authorId=57212006168</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arrieta, O.E.W. (57209248085)</t>
+          <t>Gomez, Eduardo (57212006168)</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8991,46 +8991,46 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>57201036449</t>
+          <t>57209248085</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T00012429</t>
+          <t>T00021662</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DAVID JAVIER FORTICH PEREZ</t>
+          <t>EDGARDO WILLIAM ARRIETA ORTIZ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fortich Pérez, David J.</t>
+          <t>Arrieta, O. E.W.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57201036449</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57209248085</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fortich-Pérez, David (57201036449)</t>
+          <t>Arrieta, O. E.W. (57209248085)</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -9058,10 +9058,10 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -9106,10 +9106,10 @@
         <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
         <v>0</v>
@@ -9127,44 +9127,44 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>58618811100</t>
+          <t>57201036449</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T00000083</t>
+          <t>T00012429</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DANILO LUSBIN ARIZA RUA</t>
+          <t>DAVID JAVIER FORTICH PEREZ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CIENCIAS BÁSICAS</t>
+          <t>ESCUELA DE NEGOCIOS, LEYES Y SOCIEDAD</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ariza-Rua, Danilo Lusbin</t>
+          <t>Fortich Pérez, David J.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=58618811100</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57201036449</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ariza-Rua, Danilo Lusbin (58618811100)</t>
+          <t>Fortich-Pérez, David J. (57201036449)</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -9185,16 +9185,16 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -9233,16 +9233,16 @@
         <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="n">
         <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="n">
         <v>0</v>
@@ -9254,37 +9254,37 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>58523557700</t>
+          <t>58618811100</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T00002456</t>
+          <t>T00000083</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ALFREDO MIGUEL ABUCHAR CURI</t>
+          <t>DANILO LUSBIN ARIZA RUA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>CIENCIAS BÁSICAS</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Abuchar-Curi, Alfredo Miguel</t>
+          <t>Ariza-Rua, Danilo Lusbin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=58523557700</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=58618811100</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Abuchar-Curi, Alfredo Miguel (58523557700)</t>
+          <t>Ariza-Rúa, Danilo Lusbin (58618811100)</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -9306,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9321,13 +9321,13 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y70" t="n">
         <v>0</v>
@@ -9357,19 +9357,19 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF70" t="n">
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ70" t="n">
         <v>0</v>
@@ -9381,37 +9381,37 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>57216868622</t>
+          <t>58523557700</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T00040585</t>
+          <t>T00002456</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ADOLFO BALTAR MORENO</t>
+          <t>ALFREDO MIGUEL ABUCHAR CURI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
+          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Baltar-Moreno, Adolfo</t>
+          <t>Abuchar-Curi, Alfredo Miguel</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57216868622</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=58523557700</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moreno, Adolfo Baltar (57216868622)</t>
+          <t>Abuchar-Curi, Alfredo Miguel (58523557700)</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -9454,10 +9454,10 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -9469,22 +9469,22 @@
         <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -9493,65 +9493,65 @@
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>57215557867</t>
+          <t>57216868622</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T00057454</t>
+          <t>T00040585</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CARLOS HUMBERTO GUALDRON GARCIA</t>
+          <t>ADOLFO BALTAR MORENO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ESCUELA DE INGENIERÍA, ARQUITECTURA Y DISEÑO</t>
+          <t>ESCUELA DE TRANSFORMACIÓN DIGITAL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gualdrón, Carlos</t>
+          <t>Baltar-Moreno, Adolfo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=57215557867</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57216868622</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gualdron, Carlos (57215557867)</t>
+          <t>Baltar-Moreno, Adolfo (57216868622)</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
         <v>0</v>
@@ -9584,68 +9584,68 @@
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" t="n">
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
         <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI72" t="n">
         <v>1</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>58917134900</t>
+          <t>57215557867</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T00035572</t>
+          <t>T00057454</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JEFFERSON ANDRES PIEDRAHITA GONZALEZ</t>
+          <t>CARLOS HUMBERTO GUALDRON GARCIA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9655,17 +9655,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Piedrahita, Jefferson Marulanda</t>
+          <t>Gualdrón, Carlos</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/authid/detail.uri?authorId=58917134900&amp;origin=recordpage</t>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57215557867</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Piedrahita, Jefferson (58917134900)</t>
+          <t>Gualdrón, Carlos G. (57215557867)</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -9678,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9702,7 +9702,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
@@ -9714,10 +9714,10 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -9732,10 +9732,10 @@
         <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -9744,10 +9744,10 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>1</v>
@@ -9756,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Arraut, Luis (58153979500)</t>
+          <t>Arraut, Luis Carlos (58153979500)</t>
         </is>
       </c>
       <c r="H74" t="n">

--- a/MidataMiScript.xlsx
+++ b/MidataMiScript.xlsx
@@ -1798,10 +1798,10 @@
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1861,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
         <v>3</v>
@@ -2058,7 +2058,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2115,10 +2115,10 @@
         <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
         <v>5</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -5375,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -5417,16 +5417,16 @@
         <v>1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG39" t="n">
         <v>3</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>4</v>
       </c>
       <c r="AH39" t="n">
         <v>2</v>
